--- a/excel DB format/departments.xlsx
+++ b/excel DB format/departments.xlsx
@@ -1,38 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eugene/Desktop/Project/educore/excel DB format/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bf57cd07bc147711/Desktop/project/educore/excel DB format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE1E463-B82E-E74A-A272-83E5DF4E4309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{4CE1E463-B82E-E74A-A272-83E5DF4E4309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37E75A23-3CAF-4B8D-958E-BF143E4FE50D}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="660" windowWidth="28500" windowHeight="16100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>name</t>
   </si>
@@ -101,13 +89,16 @@
   </si>
   <si>
     <t>Medcine and Surgery</t>
+  </si>
+  <si>
+    <t>Food Science and Technology</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -651,15 +642,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{070EF7BD-9A72-9E49-8AD5-5D6A8CA72691}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="34.1640625" customWidth="1"/>
+    <col min="2" max="2" width="34.1796875" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -670,7 +661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -681,7 +672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -692,7 +683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -703,7 +694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -714,7 +705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -725,7 +716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -736,7 +727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -747,7 +738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -758,7 +749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -769,7 +760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -780,7 +771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -791,7 +782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -802,7 +793,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -813,7 +804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -824,7 +815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -835,7 +826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -846,7 +837,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -857,7 +848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -868,7 +859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -879,7 +870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3">
       <c r="A21" s="2" t="s">
         <v>22</v>
       </c>
@@ -888,6 +879,17 @@
       </c>
       <c r="C21">
         <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
